--- a/templates/datenelement-erhebung.xlsx
+++ b/templates/datenelement-erhebung.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Datenelemente" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Datennutzung" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Codelisten" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Codes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Codelisten" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,10 +45,14 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +69,11 @@
         <fgColor rgb="001A5DAB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -94,8 +104,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -170,6 +183,236 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MiHUB</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Kurze freie ID je Zeile (z. B. DE-001). Dient nur zur Verknüpfung mit den Blättern »Datennutzung« und »Codes«. Zeilen mit ID 'BEISPIEL' werden beim Import ignoriert.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Klinisch verständliche deutsche Kurzbezeichnung (z. B. 'Rauchstatus').</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Was genau wird gemessen/dokumentiert? 1–3 Sätze; Skala, Zeitraum, Ein-/Ausschluss.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Versorgungsphase — aus der Liste wählen. 'Andere' → Spalte »Phase_falls_andere« nutzen.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>NSCLC, SCLC, lung_cancer_any oder 'NSCLC,SCLC'. Vorschlag — Freitext erlaubt.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Welcher Werttyp wird erfasst? Laienverständliche Auswahl; das MI-Team mappt auf FHIR-Typen.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Wie oft pro Patient:in? Aus der Liste wählen.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>UCUM-Einheit, falls Zahl/Dosis (z. B. mg, mm, %). Vorschlag — Freitext erlaubt; sonst leer.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Wann/durch welches Ereignis wird erfasst? (z. B. 'bei jeder Vorstellung').</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Erhebungsfrequenz. Vorschlag — Freitext erlaubt (z. B. per-encounter, Q3M).</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Primär verantwortliche Rolle. Vorschlag — Freitext erlaubt. Mehrere Rollen/Systeme: Blatt »Datennutzung«.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Nur falls codierter Begriff: Verbindlichkeit der Codeliste. Im Zweifel leer (MI-Team).</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Status der Standard-Codierung. Im Zweifel leer lassen (MI-Team).</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Primäres Ziel-Standard-Mapping (z. B. fhir-mii-kds, obds, kbv-mio). Optional; MI-Team ergänzt.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Belegende Leitlinie/Quelle — aus der Liste wählen (Pflicht).</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Kapitel / Empfehlungs-Nr. / Tabelle in der Quelle (Pflicht).</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Empfehlungsgrad lt. Leitlinie (A/B/0/EK/Statement/n/a). Optional.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidenzlevel (1a…4, n/a). Vorschlag — Freitext erlaubt. Optional.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Beziehungen zu anderen Elementen, Sensitivitäts-Hinweise, offene Fragen.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Name + Klinik/Fachgesellschaft für Rückfragen. Optional.</t>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>BEISPIELZEILE — wird beim Import IGNORIERT (lokale ID beginnt mit 'BEISPIEL').
+Sie können sie löschen oder einfach stehen lassen. Eigene Einträge in die Zeilen darunter (DE-001, DE-002, …).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MiHUB</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Kurze freie ID je Zeile (z. B. DE-001). Dient nur zur Verknüpfung mit den Blättern »Datennutzung« und »Codes«. Zeilen mit ID 'BEISPIEL' werden beim Import ignoriert.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Nur zur Orientierung — welches Datenelement (Bezeichnung).</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>WO wird das Datenelement genutzt (Systemklasse)? Aus der Liste wählen.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Konkreter Produktname, v. a. bei 'Sonstiges' (z. B. 'Onkostar').</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>WER nutzt es in diesem System (Rolle)? Vorschlag — Freitext erlaubt.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>WIE wird es genutzt? (erfasst/gelesen/…). Aus der Liste wählen.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Versorgungssektor dieses Datenflusses.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Ist die Nutzung in diesem System verpflichtend (z. B. Meldepflicht)?</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Beziehungen zu anderen Elementen, Sensitivitäts-Hinweise, offene Fragen.</t>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>BEISPIELZEILE — wird beim Import IGNORIERT (lokale ID beginnt mit 'BEISPIEL').
+Sie können sie löschen oder einfach stehen lassen. Eigene Einträge in die Zeilen darunter (DE-001, DE-002, …).</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>BEISPIELZEILE — wird beim Import IGNORIERT (lokale ID beginnt mit 'BEISPIEL').
+Sie können sie löschen oder einfach stehen lassen. Eigene Einträge in die Zeilen darunter (DE-001, DE-002, …).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MiHUB</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Kurze freie ID je Zeile (z. B. DE-001). Dient nur zur Verknüpfung mit den Blättern »Datennutzung« und »Codes«. Zeilen mit ID 'BEISPIEL' werden beim Import ignoriert.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Nur zur Orientierung — welches Datenelement (Bezeichnung).</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Codesystem des Codes — aus der Liste wählen (snomed-ct, loinc, icd-10-gm, …). Unbekannt? Zeile leer lassen, das MI-Team recherchiert.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Der Code im gewählten Terminologie-System (z. B. SNOMED 77176002).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Klartext/Anzeigetext zum Code (z. B. 'Smoker').</t>
+      </text>
+    </comment>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>BEISPIELZEILE — wird beim Import IGNORIERT (lokale ID beginnt mit 'BEISPIEL').
+Sie können sie löschen oder einfach stehen lassen. Eigene Einträge in die Zeilen darunter (DE-001, DE-002, …).</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>BEISPIELZEILE — wird beim Import IGNORIERT (lokale ID beginnt mit 'BEISPIEL').
+Sie können sie löschen oder einfach stehen lassen. Eigene Einträge in die Zeilen darunter (DE-001, DE-002, …).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,11 +704,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B20"/>
+  <dimension ref="B1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,83 +724,83 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mit dieser Mappe können klinische Expert:innen neue Datenelemente für den Lungenkrebs-Patientenpfad vorschlagen — ohne GitHub, ohne YAML.</t>
+          <t>Mit dieser Mappe schlagen klinische Expert:innen neue Datenelemente für den Lungenkrebs-Patientenpfad vor — ohne GitHub, ohne YAML. Das MI-Team übernimmt danach die technische Umsetzung (Codes, FHIR-Mappings) und bittet Sie um inhaltliche Bestätigung.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Das MI-Team übernimmt anschließend die technische Umsetzung (Codes, FHIR-Mappings) und bittet Sie, das Ergebnis inhaltlich zu bestätigen.</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Die Blätter dieser Mappe</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>So füllen Sie die Mappe aus:</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>• »Datenelemente« — eine Zeile je Datenelement (Hauptblatt).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1. Blatt »Datenelemente«: eine Zeile je Datenelement. Pflichtspalten sind rot hinterlegt und mit * markiert. Felder mit Dropdown bitte aus der Liste wählen.</t>
+          <t>• »Datennutzung« — WO (System) · WER (Rolle) · WIE (Nutzung); mehrere Zeilen je Element.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2. Vergeben Sie je Zeile eine kurze »lokale ID« (z. B. DE-001) — sie dient nur dazu, die Datennutzung im zweiten Blatt zuzuordnen.</t>
+          <t>• »Codes« (optional) — bekannte Codes je Element, inkl. Terminologie-System (Dropdown).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3. Blatt »Datennutzung«: WO (System) · WER (Rolle) · WIE (Nutzung) wird das Datenelement genutzt? Mehrere Zeilen je Datenelement sind möglich und erwünscht.</t>
+          <t>• »Codelisten« — ausgeblendet; speist nur die Dropdowns (bitte nicht bearbeiten).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>4. Felder, zu denen Sie nichts beitragen können (z. B. SNOMED-Codes), dürfen leer bleiben — das MI-Team recherchiert sie.</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Legende</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Beispiel »Rauchstatus« (Datennutzung):</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>• Spalten mit * und rosa Hintergrund sind PFLICHT.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • PVS · Hausärzt:in · erfasst (ambulant)</t>
+          <t>• Die erste, grau-kursive Zeile (lokale ID = BEISPIEL) ist ein BEISPIEL und wird beim Import IGNORIERT — gerne überschreiben oder löschen.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • KIS · Onkolog:in · gelesen (stationär)</t>
+          <t>• Felder mit Dropdown: Pfeil rechts in der Zelle. Manche Listen sind verbindlich, andere nur Vorschläge (dann ist auch Freitext erlaubt).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Forschungs-DWH/DIZ · Forscher:in · Forschung/Sekundärnutzung</t>
+          <t>• Erklärung je Spalte: Mauszeiger über die Kopfzeile (rotes Eck = Kommentar).</t>
         </is>
       </c>
     </row>
@@ -565,26 +808,71 @@
       <c r="B16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Andere Wege beizutragen: GitHub-Issue-Formular (online) oder YAML+Pull-Request (technisch). Siehe CONTRIBUTING.md / docs/howto-add-element.md.</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>So füllen Sie aus</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1. »Datenelemente«: je Element eine Zeile; Pflichtfelder ausfüllen, Dropdowns nutzen.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Beiträge erfolgen unter CC BY 4.0. Bitte keine personenbezogenen / realen Patientendaten eintragen — nur die abstrakte Datenelement-Definition.</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2. Vergeben Sie je Zeile eine kurze »lokale ID« (z. B. DE-001) — sie verknüpft die Blätter »Datennutzung« und »Codes« mit dem Datenelement.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Kontakt: digital-health@tu-dresden.de</t>
+          <t>3. Optional »Datennutzung« und »Codes« je lokale ID befüllen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>4. Was Sie nicht wissen (z. B. SNOMED-Codes, Standard-Mapping), darf leer bleiben — das MI-Team recherchiert es.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>5. Mappe an digital-health@tu-dresden.de senden oder an ein GitHub-Issue anhängen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Die ausgefüllte Beispielzeile »Rauchstatus« in jedem Blatt zeigt eine vollständige Erfassung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Beiträge erfolgen unter CC BY 4.0. Bitte KEINE personenbezogenen / realen Patientendaten eintragen — nur die abstrakte Datenelement-Definition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Andere Wege: GitHub-Issue-Formular (online) oder YAML+Pull-Request (technisch) — siehe CONTRIBUTING.md. Kontakt: digital-health@tu-dresden.de</t>
         </is>
       </c>
     </row>
@@ -599,33 +887,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>lokale_ID*</t>
@@ -688,17 +976,17 @@
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>Codierungs-Vorschläge</t>
+          <t>Binding-Stärke</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>Binding-Stärke</t>
+          <t>Standard-Bindungs-Status</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
         <is>
-          <t>Standard-Anbindung_Hinweis</t>
+          <t>Standard-Mapping_(primär)</t>
         </is>
       </c>
       <c r="P1" s="5" t="inlineStr">
@@ -735,988 +1023,1102 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
+          <t>BEISPIEL</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Rauchstatus</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Aktueller Tabakkonsumstatus inkl. E-Zigarette und Passivrauchexposition.</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Onkologische Nachsorge (kurativ behandelt)</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>NSCLC,SCLC</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Codierter Begriff aus Liste (SNOMED/ICD/LOINC)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Genau einmal (Pflicht)</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>bei jeder Vorstellung</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>per-encounter</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Onkolog:in</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>mapped</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>fhir-mii-kds</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>S3-LL Lungenkarzinom</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>Empf. 16.3</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIELZEILE — wird beim Import ignoriert; bitte überschreiben oder löschen.</t>
+        </is>
+      </c>
+      <c r="U2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
           <t>DE-001</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
-      <c r="Q2" s="6" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="P3" s="7" t="n"/>
+      <c r="Q3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>DE-002</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="J3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
-      <c r="P3" s="6" t="n"/>
-      <c r="Q3" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+      <c r="P4" s="7" t="n"/>
+      <c r="Q4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>DE-003</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>DE-004</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="P5" s="6" t="n"/>
-      <c r="Q5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="P6" s="7" t="n"/>
+      <c r="Q6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>DE-005</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="P7" s="7" t="n"/>
+      <c r="Q7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>DE-006</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
+      <c r="Q8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>DE-007</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="P9" s="7" t="n"/>
+      <c r="Q9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>DE-008</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>DE-009</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="P11" s="7" t="n"/>
+      <c r="Q11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>DE-010</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>DE-011</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>DE-012</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>DE-013</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>DE-014</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>DE-015</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="P17" s="7" t="n"/>
+      <c r="Q17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>DE-016</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>DE-017</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
+      <c r="P19" s="7" t="n"/>
+      <c r="Q19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>DE-018</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="P20" s="7" t="n"/>
+      <c r="Q20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>DE-019</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="P21" s="7" t="n"/>
+      <c r="Q21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>DE-020</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="P22" s="7" t="n"/>
+      <c r="Q22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>DE-021</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="P23" s="7" t="n"/>
+      <c r="Q23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>DE-022</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
-      <c r="Q23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="J24" s="7" t="n"/>
+      <c r="L24" s="7" t="n"/>
+      <c r="P24" s="7" t="n"/>
+      <c r="Q24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>DE-023</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
-      <c r="Q24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="P25" s="7" t="n"/>
+      <c r="Q25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>DE-024</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="L26" s="7" t="n"/>
+      <c r="P26" s="7" t="n"/>
+      <c r="Q26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>DE-025</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>DE-026</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
+      <c r="Q28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>DE-027</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="J29" s="7" t="n"/>
+      <c r="L29" s="7" t="n"/>
+      <c r="P29" s="7" t="n"/>
+      <c r="Q29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>DE-028</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>DE-029</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="P31" s="7" t="n"/>
+      <c r="Q31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>DE-030</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="P32" s="7" t="n"/>
+      <c r="Q32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>DE-031</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="6" t="n"/>
-      <c r="J32" s="6" t="n"/>
-      <c r="L32" s="6" t="n"/>
-      <c r="P32" s="6" t="n"/>
-      <c r="Q32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="P33" s="7" t="n"/>
+      <c r="Q33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>DE-032</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="P34" s="7" t="n"/>
+      <c r="Q34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>DE-033</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
-      <c r="L34" s="6" t="n"/>
-      <c r="P34" s="6" t="n"/>
-      <c r="Q34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="P35" s="7" t="n"/>
+      <c r="Q35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>DE-034</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="J35" s="6" t="n"/>
-      <c r="L35" s="6" t="n"/>
-      <c r="P35" s="6" t="n"/>
-      <c r="Q35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="P36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>DE-035</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-      <c r="P36" s="6" t="n"/>
-      <c r="Q36" s="6" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="P37" s="7" t="n"/>
+      <c r="Q37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>DE-036</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="P38" s="7" t="n"/>
+      <c r="Q38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>DE-037</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="6" t="n"/>
-      <c r="J38" s="6" t="n"/>
-      <c r="L38" s="6" t="n"/>
-      <c r="P38" s="6" t="n"/>
-      <c r="Q38" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="P39" s="7" t="n"/>
+      <c r="Q39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>DE-038</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="L39" s="6" t="n"/>
-      <c r="P39" s="6" t="n"/>
-      <c r="Q39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="P40" s="7" t="n"/>
+      <c r="Q40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>DE-039</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="6" t="n"/>
-      <c r="J40" s="6" t="n"/>
-      <c r="L40" s="6" t="n"/>
-      <c r="P40" s="6" t="n"/>
-      <c r="Q40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="P41" s="7" t="n"/>
+      <c r="Q41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>DE-040</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="L41" s="6" t="n"/>
-      <c r="P41" s="6" t="n"/>
-      <c r="Q41" s="6" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="P42" s="7" t="n"/>
+      <c r="Q42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>DE-041</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
-      <c r="P42" s="6" t="n"/>
-      <c r="Q42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="P43" s="7" t="n"/>
+      <c r="Q43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>DE-042</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
-      <c r="J43" s="6" t="n"/>
-      <c r="L43" s="6" t="n"/>
-      <c r="P43" s="6" t="n"/>
-      <c r="Q43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="P44" s="7" t="n"/>
+      <c r="Q44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>DE-043</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="6" t="n"/>
-      <c r="J44" s="6" t="n"/>
-      <c r="L44" s="6" t="n"/>
-      <c r="P44" s="6" t="n"/>
-      <c r="Q44" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="P45" s="7" t="n"/>
+      <c r="Q45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>DE-044</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="6" t="n"/>
-      <c r="J45" s="6" t="n"/>
-      <c r="L45" s="6" t="n"/>
-      <c r="P45" s="6" t="n"/>
-      <c r="Q45" s="6" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="P46" s="7" t="n"/>
+      <c r="Q46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>DE-045</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
-      <c r="J46" s="6" t="n"/>
-      <c r="L46" s="6" t="n"/>
-      <c r="P46" s="6" t="n"/>
-      <c r="Q46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="P47" s="7" t="n"/>
+      <c r="Q47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>DE-046</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
-      <c r="J47" s="6" t="n"/>
-      <c r="L47" s="6" t="n"/>
-      <c r="P47" s="6" t="n"/>
-      <c r="Q47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="P48" s="7" t="n"/>
+      <c r="Q48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>DE-047</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="6" t="n"/>
-      <c r="J48" s="6" t="n"/>
-      <c r="L48" s="6" t="n"/>
-      <c r="P48" s="6" t="n"/>
-      <c r="Q48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="P49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>DE-048</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="J49" s="6" t="n"/>
-      <c r="L49" s="6" t="n"/>
-      <c r="P49" s="6" t="n"/>
-      <c r="Q49" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
+      <c r="Q50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>DE-049</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-      <c r="P50" s="6" t="n"/>
-      <c r="Q50" s="6" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="P51" s="7" t="n"/>
+      <c r="Q51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>DE-050</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="P51" s="6" t="n"/>
-      <c r="Q51" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="P52" s="7" t="n"/>
+      <c r="Q52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>DE-051</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="J52" s="6" t="n"/>
-      <c r="L52" s="6" t="n"/>
-      <c r="P52" s="6" t="n"/>
-      <c r="Q52" s="6" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="P53" s="7" t="n"/>
+      <c r="Q53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>DE-052</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="L53" s="6" t="n"/>
-      <c r="P53" s="6" t="n"/>
-      <c r="Q53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="P54" s="7" t="n"/>
+      <c r="Q54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>DE-053</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="J54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
-      <c r="P54" s="6" t="n"/>
-      <c r="Q54" s="6" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="P55" s="7" t="n"/>
+      <c r="Q55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>DE-054</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="6" t="n"/>
-      <c r="J55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
-      <c r="P55" s="6" t="n"/>
-      <c r="Q55" s="6" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="P56" s="7" t="n"/>
+      <c r="Q56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>DE-055</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
-      <c r="J56" s="6" t="n"/>
-      <c r="L56" s="6" t="n"/>
-      <c r="P56" s="6" t="n"/>
-      <c r="Q56" s="6" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="P57" s="7" t="n"/>
+      <c r="Q57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>DE-056</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="6" t="n"/>
-      <c r="J57" s="6" t="n"/>
-      <c r="L57" s="6" t="n"/>
-      <c r="P57" s="6" t="n"/>
-      <c r="Q57" s="6" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="P58" s="7" t="n"/>
+      <c r="Q58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>DE-057</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="J58" s="6" t="n"/>
-      <c r="L58" s="6" t="n"/>
-      <c r="P58" s="6" t="n"/>
-      <c r="Q58" s="6" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="P59" s="7" t="n"/>
+      <c r="Q59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>DE-058</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="L59" s="6" t="n"/>
-      <c r="P59" s="6" t="n"/>
-      <c r="Q59" s="6" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="P60" s="7" t="n"/>
+      <c r="Q60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>DE-059</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="6" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="P61" s="7" t="n"/>
+      <c r="Q61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>DE-060</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
-      <c r="P61" s="6" t="n"/>
-      <c r="Q61" s="6" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="P62" s="7" t="n"/>
+      <c r="Q62" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation sqref="D2:D61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="13">
+    <dataValidation sqref="D2:D62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Codelisten!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$C$2:$C$12</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$D$2:$D$5</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$O$2:$O$18</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$P$2:$P$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$Q$2:$Q$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
       <formula1>=Codelisten!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$F$2:$F$11</formula1>
+    <dataValidation sqref="N2:N62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$F$2:$F$5</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$G$2:$G$7</formula1>
+    <dataValidation sqref="O2:O62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$G$2:$G$19</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$H$2:$H$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R62" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte aus der Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$I$2:$I$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$R$2:$R$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1726,21 +2128,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>lokale_ID_des_Datenelements*</t>
@@ -1788,924 +2190,1010 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIEL</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Rauchstatus</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Primärverwaltungssystem / Praxis-VS (PVS)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Hausärzt:in</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>erfasst / eingegeben</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>ambulant</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIEL — wird ignoriert</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIEL</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Rauchstatus</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Krankenhausinformationssystem (KIS/AIS)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Onkolog:in</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>gelesen / eingesehen</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="A4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="A5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="A6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="A11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
+      <c r="A15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="A16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
+      <c r="A17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="A18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
+      <c r="A19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
+      <c r="A21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
+      <c r="A22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
+      <c r="A23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
+      <c r="A24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
+      <c r="A25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
+      <c r="A26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
+      <c r="A27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
+      <c r="A28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
+      <c r="A29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
+      <c r="A30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
+      <c r="A31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
+      <c r="A32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
+      <c r="A33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
+      <c r="A34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
+      <c r="A35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
+      <c r="A36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
+      <c r="A37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
+      <c r="A38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
+      <c r="A39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="A40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
+      <c r="A41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
+      <c r="A42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
+      <c r="A43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
+      <c r="A44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
+      <c r="A45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
+      <c r="A46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
+      <c r="A47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
+      <c r="A48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
+      <c r="A49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
+      <c r="A50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
+      <c r="A51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
+      <c r="A52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
+      <c r="A53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
+      <c r="A54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="F55" s="6" t="n"/>
+      <c r="A55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
+      <c r="A56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
+      <c r="A57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
+      <c r="A58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
+      <c r="A59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
+      <c r="A60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
+      <c r="A61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
+      <c r="A62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
+      <c r="A63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
+      <c r="A64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
+      <c r="A65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
+      <c r="A66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
+      <c r="A67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
+      <c r="A68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
+      <c r="A69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
+      <c r="A70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
+      <c r="A71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
+      <c r="A72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
+      <c r="A73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
+      <c r="A74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
+      <c r="A75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
+      <c r="A76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
+      <c r="A77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
+      <c r="A78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="C79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
+      <c r="A79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
+      <c r="A80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
+      <c r="A81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
+      <c r="A82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n"/>
-      <c r="C83" s="6" t="n"/>
-      <c r="F83" s="6" t="n"/>
+      <c r="A83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="F83" s="7" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="F84" s="6" t="n"/>
+      <c r="A84" s="7" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="F84" s="7" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
+      <c r="A85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="F85" s="7" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
+      <c r="A86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
+      <c r="A87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
+      <c r="A88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
+      <c r="A89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="F89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
+      <c r="A90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n"/>
-      <c r="C91" s="6" t="n"/>
-      <c r="F91" s="6" t="n"/>
+      <c r="A91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="F91" s="7" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
+      <c r="A92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="F93" s="6" t="n"/>
+      <c r="A93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
+      <c r="A94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="F95" s="6" t="n"/>
+      <c r="A95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="F95" s="7" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="F96" s="6" t="n"/>
+      <c r="A96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="F96" s="7" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
+      <c r="A97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
+      <c r="A98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
+      <c r="A99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="F99" s="7" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
+      <c r="A100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="F100" s="7" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
+      <c r="A101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="F101" s="7" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
+      <c r="A102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="F102" s="7" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="F103" s="6" t="n"/>
+      <c r="A103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="F103" s="7" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
+      <c r="A104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="F104" s="7" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="F105" s="6" t="n"/>
+      <c r="A105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="F105" s="7" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
+      <c r="A106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="F106" s="7" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
+      <c r="A107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
+      <c r="A108" s="7" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
+      <c r="A109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="F109" s="7" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
+      <c r="A110" s="7" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="F110" s="7" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
+      <c r="A111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="F111" s="7" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="F112" s="6" t="n"/>
+      <c r="A112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="F113" s="6" t="n"/>
+      <c r="A113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="F113" s="7" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
+      <c r="A114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="F114" s="7" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="F115" s="6" t="n"/>
+      <c r="A115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="F115" s="7" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
+      <c r="A116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
+      <c r="A117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
+      <c r="A118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="n"/>
-      <c r="C119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
+      <c r="A119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
+      <c r="A120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
+      <c r="A121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
+      <c r="A122" s="7" t="n"/>
+      <c r="C122" s="7" t="n"/>
+      <c r="F122" s="7" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="n"/>
-      <c r="C123" s="6" t="n"/>
-      <c r="F123" s="6" t="n"/>
+      <c r="A123" s="7" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="F123" s="7" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="F124" s="6" t="n"/>
+      <c r="A124" s="7" t="n"/>
+      <c r="C124" s="7" t="n"/>
+      <c r="F124" s="7" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
+      <c r="A125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="F126" s="6" t="n"/>
+      <c r="A126" s="7" t="n"/>
+      <c r="C126" s="7" t="n"/>
+      <c r="F126" s="7" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="6" t="n"/>
-      <c r="C127" s="6" t="n"/>
-      <c r="F127" s="6" t="n"/>
+      <c r="A127" s="7" t="n"/>
+      <c r="C127" s="7" t="n"/>
+      <c r="F127" s="7" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
+      <c r="A128" s="7" t="n"/>
+      <c r="C128" s="7" t="n"/>
+      <c r="F128" s="7" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
+      <c r="A129" s="7" t="n"/>
+      <c r="C129" s="7" t="n"/>
+      <c r="F129" s="7" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="6" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
+      <c r="A130" s="7" t="n"/>
+      <c r="C130" s="7" t="n"/>
+      <c r="F130" s="7" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="F131" s="6" t="n"/>
+      <c r="A131" s="7" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="n"/>
-      <c r="C132" s="6" t="n"/>
-      <c r="F132" s="6" t="n"/>
+      <c r="A132" s="7" t="n"/>
+      <c r="C132" s="7" t="n"/>
+      <c r="F132" s="7" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="F133" s="6" t="n"/>
+      <c r="A133" s="7" t="n"/>
+      <c r="C133" s="7" t="n"/>
+      <c r="F133" s="7" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
+      <c r="A134" s="7" t="n"/>
+      <c r="C134" s="7" t="n"/>
+      <c r="F134" s="7" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="F135" s="6" t="n"/>
+      <c r="A135" s="7" t="n"/>
+      <c r="C135" s="7" t="n"/>
+      <c r="F135" s="7" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
+      <c r="A136" s="7" t="n"/>
+      <c r="C136" s="7" t="n"/>
+      <c r="F136" s="7" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="n"/>
-      <c r="C137" s="6" t="n"/>
-      <c r="F137" s="6" t="n"/>
+      <c r="A137" s="7" t="n"/>
+      <c r="C137" s="7" t="n"/>
+      <c r="F137" s="7" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="F138" s="6" t="n"/>
+      <c r="A138" s="7" t="n"/>
+      <c r="C138" s="7" t="n"/>
+      <c r="F138" s="7" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="n"/>
-      <c r="C139" s="6" t="n"/>
-      <c r="F139" s="6" t="n"/>
+      <c r="A139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
+      <c r="A140" s="7" t="n"/>
+      <c r="C140" s="7" t="n"/>
+      <c r="F140" s="7" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="F141" s="6" t="n"/>
+      <c r="A141" s="7" t="n"/>
+      <c r="C141" s="7" t="n"/>
+      <c r="F141" s="7" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
+      <c r="A142" s="7" t="n"/>
+      <c r="C142" s="7" t="n"/>
+      <c r="F142" s="7" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="F143" s="6" t="n"/>
+      <c r="A143" s="7" t="n"/>
+      <c r="C143" s="7" t="n"/>
+      <c r="F143" s="7" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
+      <c r="A144" s="7" t="n"/>
+      <c r="C144" s="7" t="n"/>
+      <c r="F144" s="7" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="F145" s="6" t="n"/>
+      <c r="A145" s="7" t="n"/>
+      <c r="C145" s="7" t="n"/>
+      <c r="F145" s="7" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
+      <c r="A146" s="7" t="n"/>
+      <c r="C146" s="7" t="n"/>
+      <c r="F146" s="7" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="F147" s="6" t="n"/>
+      <c r="A147" s="7" t="n"/>
+      <c r="C147" s="7" t="n"/>
+      <c r="F147" s="7" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="n"/>
-      <c r="C148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
+      <c r="A148" s="7" t="n"/>
+      <c r="C148" s="7" t="n"/>
+      <c r="F148" s="7" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="6" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
+      <c r="A149" s="7" t="n"/>
+      <c r="C149" s="7" t="n"/>
+      <c r="F149" s="7" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
+      <c r="A150" s="7" t="n"/>
+      <c r="C150" s="7" t="n"/>
+      <c r="F150" s="7" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
+      <c r="A151" s="7" t="n"/>
+      <c r="C151" s="7" t="n"/>
+      <c r="F151" s="7" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="F152" s="6" t="n"/>
+      <c r="A152" s="7" t="n"/>
+      <c r="C152" s="7" t="n"/>
+      <c r="F152" s="7" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="F153" s="6" t="n"/>
+      <c r="A153" s="7" t="n"/>
+      <c r="C153" s="7" t="n"/>
+      <c r="F153" s="7" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="6" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
+      <c r="A154" s="7" t="n"/>
+      <c r="C154" s="7" t="n"/>
+      <c r="F154" s="7" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="F155" s="6" t="n"/>
+      <c r="A155" s="7" t="n"/>
+      <c r="C155" s="7" t="n"/>
+      <c r="F155" s="7" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="n"/>
-      <c r="C156" s="6" t="n"/>
-      <c r="F156" s="6" t="n"/>
+      <c r="A156" s="7" t="n"/>
+      <c r="C156" s="7" t="n"/>
+      <c r="F156" s="7" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="6" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
+      <c r="A157" s="7" t="n"/>
+      <c r="C157" s="7" t="n"/>
+      <c r="F157" s="7" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="F158" s="6" t="n"/>
+      <c r="A158" s="7" t="n"/>
+      <c r="C158" s="7" t="n"/>
+      <c r="F158" s="7" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="6" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="F159" s="6" t="n"/>
+      <c r="A159" s="7" t="n"/>
+      <c r="C159" s="7" t="n"/>
+      <c r="F159" s="7" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="n"/>
-      <c r="C160" s="6" t="n"/>
-      <c r="F160" s="6" t="n"/>
+      <c r="A160" s="7" t="n"/>
+      <c r="C160" s="7" t="n"/>
+      <c r="F160" s="7" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="6" t="n"/>
-      <c r="C161" s="6" t="n"/>
-      <c r="F161" s="6" t="n"/>
+      <c r="A161" s="7" t="n"/>
+      <c r="C161" s="7" t="n"/>
+      <c r="F161" s="7" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="n"/>
-      <c r="C162" s="6" t="n"/>
-      <c r="F162" s="6" t="n"/>
+      <c r="A162" s="7" t="n"/>
+      <c r="C162" s="7" t="n"/>
+      <c r="F162" s="7" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="F163" s="6" t="n"/>
+      <c r="A163" s="7" t="n"/>
+      <c r="C163" s="7" t="n"/>
+      <c r="F163" s="7" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="6" t="n"/>
-      <c r="C164" s="6" t="n"/>
-      <c r="F164" s="6" t="n"/>
+      <c r="A164" s="7" t="n"/>
+      <c r="C164" s="7" t="n"/>
+      <c r="F164" s="7" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="n"/>
-      <c r="C165" s="6" t="n"/>
-      <c r="F165" s="6" t="n"/>
+      <c r="A165" s="7" t="n"/>
+      <c r="C165" s="7" t="n"/>
+      <c r="F165" s="7" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
+      <c r="A166" s="7" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="F166" s="7" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="n"/>
-      <c r="C167" s="6" t="n"/>
-      <c r="F167" s="6" t="n"/>
+      <c r="A167" s="7" t="n"/>
+      <c r="C167" s="7" t="n"/>
+      <c r="F167" s="7" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="n"/>
-      <c r="C168" s="6" t="n"/>
-      <c r="F168" s="6" t="n"/>
+      <c r="A168" s="7" t="n"/>
+      <c r="C168" s="7" t="n"/>
+      <c r="F168" s="7" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="F169" s="6" t="n"/>
+      <c r="A169" s="7" t="n"/>
+      <c r="C169" s="7" t="n"/>
+      <c r="F169" s="7" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="n"/>
-      <c r="C170" s="6" t="n"/>
-      <c r="F170" s="6" t="n"/>
+      <c r="A170" s="7" t="n"/>
+      <c r="C170" s="7" t="n"/>
+      <c r="F170" s="7" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="F171" s="6" t="n"/>
+      <c r="A171" s="7" t="n"/>
+      <c r="C171" s="7" t="n"/>
+      <c r="F171" s="7" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
+      <c r="A172" s="7" t="n"/>
+      <c r="C172" s="7" t="n"/>
+      <c r="F172" s="7" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="n"/>
-      <c r="C173" s="6" t="n"/>
-      <c r="F173" s="6" t="n"/>
+      <c r="A173" s="7" t="n"/>
+      <c r="C173" s="7" t="n"/>
+      <c r="F173" s="7" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="F174" s="6" t="n"/>
+      <c r="A174" s="7" t="n"/>
+      <c r="C174" s="7" t="n"/>
+      <c r="F174" s="7" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="n"/>
-      <c r="C175" s="6" t="n"/>
-      <c r="F175" s="6" t="n"/>
+      <c r="A175" s="7" t="n"/>
+      <c r="C175" s="7" t="n"/>
+      <c r="F175" s="7" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="6" t="n"/>
-      <c r="C176" s="6" t="n"/>
-      <c r="F176" s="6" t="n"/>
+      <c r="A176" s="7" t="n"/>
+      <c r="C176" s="7" t="n"/>
+      <c r="F176" s="7" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="n"/>
-      <c r="C177" s="6" t="n"/>
-      <c r="F177" s="6" t="n"/>
+      <c r="A177" s="7" t="n"/>
+      <c r="C177" s="7" t="n"/>
+      <c r="F177" s="7" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="6" t="n"/>
-      <c r="C178" s="6" t="n"/>
-      <c r="F178" s="6" t="n"/>
+      <c r="A178" s="7" t="n"/>
+      <c r="C178" s="7" t="n"/>
+      <c r="F178" s="7" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="n"/>
-      <c r="C179" s="6" t="n"/>
-      <c r="F179" s="6" t="n"/>
+      <c r="A179" s="7" t="n"/>
+      <c r="C179" s="7" t="n"/>
+      <c r="F179" s="7" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="6" t="n"/>
-      <c r="C180" s="6" t="n"/>
-      <c r="F180" s="6" t="n"/>
+      <c r="A180" s="7" t="n"/>
+      <c r="C180" s="7" t="n"/>
+      <c r="F180" s="7" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="n"/>
-      <c r="C181" s="6" t="n"/>
-      <c r="F181" s="6" t="n"/>
+      <c r="A181" s="7" t="n"/>
+      <c r="C181" s="7" t="n"/>
+      <c r="F181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="n"/>
+      <c r="C182" s="7" t="n"/>
+      <c r="F182" s="7" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="n"/>
+      <c r="C183" s="7" t="n"/>
+      <c r="F183" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="C2:C181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$H$2:$H$12</formula1>
+  <dataValidations count="6">
+    <dataValidation sqref="C2:C183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$J$2:$J$12</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$I$2:$I$12</formula1>
+    <dataValidation sqref="E2:E183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$Q$2:$Q$10</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$J$2:$J$5</formula1>
+    <dataValidation sqref="F2:F183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$K$2:$K$12</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Codelisten!$K$2:$K$3</formula1>
+    <dataValidation sqref="G2:G183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$L$2:$L$5</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Datenelemente!$A$2:$A$61</formula1>
+    <dataValidation sqref="H2:H183" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Ungültige Eingabe" error="Bitte einen Wert aus der Dropdown-Liste wählen." type="list" errorStyle="stop">
+      <formula1>=Codelisten!$M$2:$M$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="A2:A183" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Datenelemente!$A$2:$A$62</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2715,76 +3203,829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>lokale_ID_des_Datenelements*</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Bezeichnung_(zur_Orientierung)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Terminologie-System*</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Code*</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Anzeigetext_(Display)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIEL</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Rauchstatus</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>snomed-ct</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>77176002</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Smoker</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>BEISPIEL</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Rauchstatus</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>snomed-ct</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>8517006</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Ex-smoker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
+      <c r="D83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n"/>
+      <c r="C84" s="7" t="n"/>
+      <c r="D84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n"/>
+      <c r="C122" s="7" t="n"/>
+      <c r="D122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="n"/>
+      <c r="C123" s="7" t="n"/>
+      <c r="D123" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Codelisten!$N$2:$N$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="A2:A123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Datenelemente!$A$2:$A$62</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>tumor_entity_multi</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>datatype_laymen</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>cardinality_laymen</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>binding_strength</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>standard_binding_status</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>guideline_source</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>recommendation_grade</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>system_laymen</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>usage_laymen</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>sector_laymen</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>ja_nein</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>terminology_system</t>
+        </is>
+      </c>
+      <c r="O1" s="8" t="inlineStr">
+        <is>
+          <t>unit_suggest</t>
+        </is>
+      </c>
+      <c r="P1" s="8" t="inlineStr">
+        <is>
+          <t>frequency_suggest</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
+        <is>
+          <t>role_suggest</t>
+        </is>
+      </c>
+      <c r="R1" s="8" t="inlineStr">
+        <is>
+          <t>evidence_levels</t>
         </is>
       </c>
     </row>
@@ -2816,32 +4057,67 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>mapped</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>obds</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>S3-LL Lungenkarzinom</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Primärverwaltungssystem / Praxis-VS (PVS)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>erfasst / eingegeben</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>ambulant</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Ja</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>snomed-ct</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>per-encounter</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Onkolog:in</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1a</t>
         </is>
       </c>
     </row>
@@ -2873,32 +4149,67 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>no-standard-found</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>gekid-adt</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>S3-LL Palliativmedizin</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Krankenhausinformationssystem (KIS/AIS)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>gelesen / eingesehen</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>stationär</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Nein</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>loinc</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>mg/d</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ad-hoc</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Hausärzt:in</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1b</t>
         </is>
       </c>
     </row>
@@ -2930,27 +4241,62 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>pending-mapping</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>gematik-epa-fhir</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>S3-LL Tabakentwöhnung</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Tumordokumentationssystem</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>aktualisiert / korrigiert</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>sektorenübergreifend</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>icd-10-gm</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>einmalig</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Pflegefachperson</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2a</t>
         </is>
       </c>
     </row>
@@ -2982,27 +4328,62 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>gematik-erezept-fhir</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Onkopedia NSCLC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>EK</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Klinisches/Epidemiologisches Krebsregister</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>geprüft / freigegeben</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>häuslich / zuhause</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>icd-o-3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Palliativteam</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2b</t>
         </is>
       </c>
     </row>
@@ -3012,24 +4393,54 @@
           <t>Datum + Uhrzeit</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kbv-mio</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Onkopedia SCLC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Labor-/Pathologie-IS (LIS)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>übermittelt / ausgetauscht</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>icf</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tumorboard / MDT</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3039,24 +4450,54 @@
           <t>Zeitraum (von–bis)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>fhir-mii-kds</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>OCP Lung (AU)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Radiologie (RIS/PACS)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>gespeichert / archiviert</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Q3M</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Tumordokumentar:in</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3066,19 +4507,49 @@
           <t>Codierter Begriff aus Liste (SNOMED/ICD/LOINC)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>fhir-isik</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>AG LONKO / Survivorship</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Elektronische Patientenakte (ePA)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>abgeleitet / berechnet</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>kdl</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>/min</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Q6M</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Radiolog:in</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -3088,19 +4559,44 @@
           <t>Freitext (kurz)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fhir-r4-base</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>ESMO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Patientenportal / PRO-App</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Forschung / Sekundärnutzung</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>atc</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mo</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Q12M</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Patholog:in</t>
         </is>
       </c>
     </row>
@@ -3110,19 +4606,44 @@
           <t>Freitext (lang)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>fhir-genomics</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>ASCO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Forschungs-DWH / DIZ / FDPG</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>im Patientenportal angezeigt</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ucum</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Q3M-Y1-Y2;Q6M-Y3-Y5</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Patient:in (Selbsteinschätzung)</t>
         </is>
       </c>
     </row>
@@ -3132,19 +4653,34 @@
           <t>Dosis/Menge mit Einheit (z. B. mg)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>mcode</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>andere</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Vernetzungs-/Kooperationsplattform</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>durch Patient:in selbst erfasst</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>hl7-v3</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
     </row>
@@ -3154,14 +4690,113 @@
           <t>Verweis auf Dokument/Befund</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>openehr-archetype</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Sonstiges (bitte System benennen)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>meddra</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>omop-cdm</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>local-no-standard-binding</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Punkte</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cdisc-sdtm</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>hl7-v2</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>µmol/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>dicom-sr</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>U/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hl7-cda</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Gy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ihe-xds</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ng/mL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
